--- a/step1-validation-check.xlsx
+++ b/step1-validation-check.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step1 実装チェック" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Step1 実装チェック'!$A$1:$H$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Step1 実装チェック'!$A$1:$H$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,11 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -88,9 +83,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -458,17 +450,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,17 +675,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>英字のみ許可</t>
+          <t>英字+アポストロフィ許可</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>alpha+space</t>
+          <t>alpha+space+apostrophe</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>replace(/[^a-zA-Z\s]/g,"")</t>
+          <t>replace(/[^a-zA-Z\s']/g,"")</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -701,7 +693,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>アポストロフィ対応済み</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -742,44 +738,44 @@
       <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>姓 / Surname</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>スペース正規化</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>複数→半角1つ</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>blur時trimのみ</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>input時の正規化未実装</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>input時replace(/\s{2,}/g," ")</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>input時+blur時の両方で正規化</t>
         </is>
       </c>
     </row>
@@ -860,42 +856,46 @@
       <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>姓 / Surname</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Step1未実装</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn() Step別制御</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>appForm内.error.show検知</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>名 / Given name</t>
+          <t>姓 / Surname</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -915,17 +915,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>入力項目</t>
+          <t>ウムラウト変換</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>テキスト入力</t>
+          <t>ä→AE, ö→OE等</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>input type=text</t>
+          <t>convertUmlaut()</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -933,7 +933,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>DEU/北欧向け</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -953,17 +957,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>プレースホルダー</t>
+          <t>入力項目</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ja（例）TARO</t>
+          <t>テキスト入力</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>placeholder実装</t>
+          <t>input type=text</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -991,17 +995,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>必須項目</t>
+          <t>プレースホルダー</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>ja（例）TARO</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>required属性</t>
+          <t>placeholder実装</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1029,17 +1033,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>文字数45字以内</t>
+          <t>必須項目</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>最大45字</t>
+          <t>required</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>slice(0,45)</t>
+          <t>required属性</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1067,17 +1071,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>英字のみ許可</t>
+          <t>文字数45字以内</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>alpha+space</t>
+          <t>最大45字</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>replace(/[^a-zA-Z\s]/g,"")</t>
+          <t>slice(0,45)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1105,67 +1109,63 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>英字+アポストロフィ許可</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>alpha+space+apostrophe</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>名 / Given name</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>自動大文字変換</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>toUpperCase</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>名 / Given name</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>スペース正規化</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>複数→半角1つ</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>blur時trimのみ</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>input時の正規化未実装</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>前後スペース削除</t>
+          <t>スペース正規化</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>trim</t>
+          <t>複数→半角1つ</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>blur時trim</t>
+          <t>input時+blur時正規化</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1223,181 +1223,185 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>前後スペース削除</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>trim</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>blur時trim</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>名 / Given name</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>エラーメッセージ</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>半角英字で入力してください</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>err要素実装</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>名 / Given name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Step1未実装</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn()</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>名 / Given name</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>項目下注記</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>パスポート記載通り入力</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>.hint「※パスポート記載と同じ綴りで…」</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ミドルネーム含む注記追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>苗字チェックアラート</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>候補にない場合アラート</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>未実装</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>姓</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>苗字チェックアラート</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>候補にない場合アラート</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>苗字辞書なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>名</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>項目下注記</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>パスポート記載通り入力</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>別名の有無</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>ボタン選択</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>はい/いいえ</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>radio aliasYes/No</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>苗字辞書データが必要</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1417,17 +1421,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>必須/デフォルト</t>
+          <t>ボタン選択</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>「別名はありません」</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>aliasNo checked</t>
+          <t>radio aliasYes/No</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1455,17 +1459,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>必須/デフォルト</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>※上記以外の名前…</t>
+          <t>「別名はありません」</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>.note要素</t>
+          <t>aliasNo checked</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1493,17 +1497,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Yes→入力欄表示</t>
+          <t>注記</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>collapsible show</t>
+          <t>※上記以外の名前…</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>.note要素</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1521,7 +1525,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>姓(別名)</t>
+          <t>別名の有無</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1531,17 +1535,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>入力項目</t>
+          <t>Yes→入力欄表示</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>テキスト</t>
+          <t>collapsible show</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>input実装</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1569,17 +1573,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>プレースホルダー</t>
+          <t>入力項目</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>（例）YAMADA</t>
+          <t>テキスト</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>placeholder実装</t>
+          <t>input実装</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1607,63 +1611,63 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>必須/45字/英字のみ/大文字/trim</t>
+          <t>プレースホルダー</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>（例）YAMADA</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>placeholder実装</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>姓(別名)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>必須/45字/英字+アポストロフィ/大文字/trim</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>全バリデーション</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>setupNameField</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>姓(別名)</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>スペース正規化</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>複数→1つ</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1683,63 +1687,63 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>スペース正規化</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>複数→1つ</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>input時+blur時</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>姓(別名)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>エラー表示</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>半角英字で入力してください</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>err要素</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>姓(別名)</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1749,7 +1753,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>名(別名)</t>
+          <t>姓(別名)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1759,17 +1763,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>入力項目</t>
+          <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>テキスト</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>input実装</t>
+          <t>updateBtn()</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1797,17 +1801,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>プレースホルダー</t>
+          <t>入力項目</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>（例）HIROSHI</t>
+          <t>テキスト</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>placeholder実装</t>
+          <t>input実装</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1835,63 +1839,63 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>必須/45字/英字のみ/大文字/trim</t>
+          <t>プレースホルダー</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>（例）HIROSHI</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>placeholder実装</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>名(別名)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>必須/45字/英字+アポストロフィ/大文字/trim</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>全バリデーション</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>setupNameField</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>名(別名)</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>スペース正規化</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>複数→1つ</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1911,139 +1915,143 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>スペース正規化</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>複数→1つ</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>input時+blur時</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>名(別名)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>エラー表示</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>半角英字で入力してください</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>err要素</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>名(別名)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn()</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>姓(別名)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>苗字チェックアラート</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>候補にない場合アラート</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>未実装</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>姓(別名)</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>苗字チェックアラート</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>候補にない場合アラート</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>性別</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>ボタン形式</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>男性/女性</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>radio実装</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>苗字辞書データが必要</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2063,63 +2071,63 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>ボタン形式</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>男性/女性</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>radio実装</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>必須/未選択デフォルト</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>性別</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>DEU時Unspecified追加</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>ドイツ選択で3択</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2129,7 +2137,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>生年月日</t>
+          <t>性別</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2139,17 +2147,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>プルダウン</t>
+          <t>DEU時Unspecified追加</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Year/Month/Day</t>
+          <t>ドイツ選択で3択</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>select実装</t>
+          <t>動的追加/削除実装</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2157,7 +2165,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>国籍変更時にDOM操作</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2177,17 +2189,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>必須/デフォルト</t>
+          <t>プルダウン</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Year年Month月Day日</t>
+          <t>Year/Month/Day</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>select実装</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2215,67 +2227,63 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>必須/デフォルト</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Year年Month月Day日</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>生年月日</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
           <t>未来日制御</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>checkDob</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>生年月日</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>エラー+月日リセット</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>アラート+リセット</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示あり</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>月日リセット要確認</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2285,7 +2293,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>国籍</t>
+          <t>生年月日</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2295,17 +2303,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>プルダウン</t>
+          <t>エラー+月日リセット</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ESTA対象国</t>
+          <t>アラート+リセット</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>custom-select</t>
+          <t>Month/Dayを空にリセット</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2313,7 +2321,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未来日時にMonth/Day=""</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2333,63 +2345,63 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>プルダウン</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>ESTA対象国</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>custom-select</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>国籍</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
           <t>必須/デフォルトJPN</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>JAPAN(JPN)</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>value=JPN</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>国籍</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>未選択時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2399,7 +2411,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>個人識別番号(NID)</t>
+          <t>国籍</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2409,17 +2421,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>対象21カ国で表示</t>
+          <t>未選択時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>BEL,BRN,CHL...</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>ID_REQUIRED_NATIONS</t>
+          <t>updateBtn()で電話種別も含め制御</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2447,17 +2459,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>任意/プレースホルダー</t>
+          <t>対象21カ国で表示</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>空欄でも可</t>
+          <t>BEL,BRN,CHL...</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>ID_REQUIRED_NATIONS</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2485,17 +2497,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>任意/プレースホルダー</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>※パスポートを除く…</t>
+          <t>空欄でも可</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>personalIdHint</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2523,17 +2535,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>英数字のみ/大文字/半角変換</t>
+          <t>注記</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>※パスポートを除く…</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>personalIdHint</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2561,147 +2573,143 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>英数字のみ/大文字/半角変換</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>個人識別番号(NID)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
           <t>スペース除去</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>全除去</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>replace(/\s/g,"")</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>個人識別番号(NID)</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>最大14文字</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>文字数制限</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>国別maxで制御</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>14固定ではなく国別</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>デフォルトmax=14に統一</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>国別max未設定時は14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>個人識別番号(NID)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>エラーメッセージ</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>半角英数字で入力してください</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>「入力形式に誤りがあります」</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>文言が仕様と異なる</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>個人識別番号(NID)</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>文言修正済み</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2711,7 +2719,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>個人識別番号(TWN)</t>
+          <t>個人識別番号(NID)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2721,17 +2729,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>TWN選択時表示/必須</t>
+          <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>英字1+数字9=10文字</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>ID_REQUIRED_MAP TWN</t>
+          <t>updateBtn()</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2759,115 +2767,111 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>TWN選択時表示/必須</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>英字1+数字9=10文字</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>ID_REQUIRED_MAP TWN</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>個人識別番号(TWN)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>プレースホルダー/注記</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>(例)A123456789</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>個人識別番号(TWN)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>エラーメッセージ</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>10桁の半角英数字で…</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>汎用エラー文</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>文言が仕様と異なる</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>申請者情報</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>個人識別番号(TWN)</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>10桁の半角英数字で入力してください</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>文言修正済み</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>連絡先情報</t>
+          <t>申請者情報</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>メールアドレス</t>
+          <t>個人識別番号(TWN)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2877,17 +2881,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>入力/必須/100字/形式チェック</t>
+          <t>チェックデジット検証</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>全バリデーション</t>
+          <t>加重合計mod10=0</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>TWN check digit実装</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2895,17 +2899,21 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>不正CD時エラー表示</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>連絡先情報</t>
+          <t>申請者情報</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>メールアドレス</t>
+          <t>個人識別番号(TWN)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2915,17 +2923,17 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>※申請結果をメールにて…</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>.note実装</t>
+          <t>updateBtn()</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2953,12 +2961,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>ハイフン変換/trim</t>
+          <t>入力/必須/100字/形式チェック</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>全角→半角/trim</t>
+          <t>全バリデーション</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -2991,17 +2999,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>エラー表示</t>
+          <t>注記</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>メールアドレスを正しく…</t>
+          <t>※申請結果をメールにて…</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>errEmail1</t>
+          <t>.note実装</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3012,42 +3020,42 @@
       <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>連絡先情報</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>メールアドレス</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>ハイフン変換/trim</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>全角→半角/trim</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3057,7 +3065,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>メール(確認)</t>
+          <t>メールアドレス</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3067,17 +3075,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>一致チェック</t>
+          <t>エラー表示</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>email1と比較</t>
+          <t>メールアドレスを正しく…</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>errEmailMatch</t>
+          <t>errEmail1</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3095,7 +3103,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>メール(確認)</t>
+          <t>メールアドレス</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3105,17 +3113,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>※確認のため再度…</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>.note実装</t>
+          <t>updateBtn()</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3143,17 +3151,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>スペース除去/ハイフン変換</t>
+          <t>一致チェック</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>全処理</t>
+          <t>email1と比較</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>errEmailMatch</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3164,42 +3172,42 @@
       <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>連絡先情報</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>メール(確認)</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>※確認のため再度…</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>.note実装</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3209,7 +3217,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>電話番号(国番号)</t>
+          <t>メール(確認)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3219,17 +3227,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>デフォルトJAPAN(+81)</t>
+          <t>スペース除去/ハイフン変換</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>プルダウン</t>
+          <t>全処理</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>custom-select phone</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3247,7 +3255,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>メール(確認)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3257,17 +3265,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>必須/20字/数字のみ</t>
+          <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>digits+slice(0,20)</t>
+          <t>updateBtn()</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3285,7 +3293,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>電話番号(国番号)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3295,17 +3303,17 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>全角→半角/スペースハイフン除去</t>
+          <t>デフォルトJAPAN(+81)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>変換処理</t>
+          <t>プルダウン</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>toHalf+replace</t>
+          <t>custom-select phone</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3333,17 +3341,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>必須/20字/数字のみ</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>※先頭の0は省略…</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>.hint実装</t>
+          <t>digits+slice(0,20)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3354,42 +3362,42 @@
       <c r="H75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>連絡先情報</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>電話番号</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>全角→半角/スペースハイフン除去</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>変換処理</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>toHalf+replace</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3399,7 +3407,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>電話種別</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3409,17 +3417,17 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>プルダウン4択</t>
+          <t>注記</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>自宅/勤務先/携帯/その他</t>
+          <t>※先頭の0は省略…</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>select実装</t>
+          <t>.hint実装</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3437,7 +3445,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>電話種別</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3447,17 +3455,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>必須/デフォルト未選択</t>
+          <t>先頭0除去</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>選択してください</t>
+          <t>blur時data-cleaned保存</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>dataset.cleaned</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3465,55 +3473,59 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>登録用に0除去値を保持</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>連絡先情報</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>電話種別</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>未選択時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>エラー時ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>disabled</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn()</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>住所情報</t>
+          <t>連絡先情報</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>電話種別</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3523,17 +3535,17 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>入力/必須/10字/数字のみ</t>
+          <t>プルダウン4択</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>自宅/勤務先/携帯/その他</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>select実装</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3546,12 +3558,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>住所情報</t>
+          <t>連絡先情報</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>電話種別</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3561,12 +3573,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>注記/検索リンク</t>
+          <t>必須/デフォルト未選択</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>ハイフン除く/郵便局URL</t>
+          <t>選択してください</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3584,12 +3596,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>住所情報</t>
+          <t>連絡先情報</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>電話種別</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3599,17 +3611,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>自動入力</t>
+          <t>未選択時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>7桁で都道府県/市区町村</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>zipcloud API</t>
+          <t>updateBtn()でphoneType空判定</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3637,17 +3649,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>不正番号アラート</t>
+          <t>入力/必須/10字/数字のみ</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>間違いありませんか？</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>errPostalInvalid</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3658,42 +3670,42 @@
       <c r="H83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>住所情報</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>郵便番号</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>注記/検索リンク</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ハイフン除く/郵便局URL</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3703,7 +3715,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>国</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3713,17 +3725,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須/デフォルトJPN</t>
+          <t>自動入力</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>JAPAN(JPN)</t>
+          <t>7桁で都道府県/市区町村</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>custom-select</t>
+          <t>zipcloud API</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3741,7 +3753,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>都道府県</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3751,17 +3763,17 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>入力/必須/60字</t>
+          <t>不正番号アラート</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>全バリデーション</t>
+          <t>間違いありませんか？</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>setupAddrField(60,False)</t>
+          <t>errPostalInvalid</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3779,7 +3791,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>都道府県</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3789,17 +3801,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>英字+記号/大文字/半角/スペース/trim</t>
+          <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>全変換</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>updateBtn()</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3817,73 +3829,73 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
+          <t>国</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>プルダウン/必須/デフォルトJPN</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>JAPAN(JPN)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>custom-select</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>都道府県</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>エラー表示</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>エラーメッセージ</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>.red-hint又はerr要素</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>都道府県</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>入力/必須/60字</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>全バリデーション</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>setupAddrField(60,False)</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3893,7 +3905,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>市区町村</t>
+          <t>都道府県</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3903,17 +3915,17 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>入力/必須/70字</t>
+          <t>英字+記号/大文字/半角/スペース/trim</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>全バリデーション</t>
+          <t>全変換</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>setupAddrField(70,True)</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3931,7 +3943,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>市区町村</t>
+          <t>都道府県</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3941,17 +3953,17 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>英字+記号/大文字/半角/スペース/trim</t>
+          <t>エラー表示</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>全変換</t>
+          <t>エラーメッセージ</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>.red-hint又はerr要素</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3969,73 +3981,73 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>エラー時ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn()</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>市区町村</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>エラー表示</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>エラーメッセージ</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>.red-hint又はerr要素</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>市区町村</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>入力/必須/70字</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>全バリデーション</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>setupAddrField(70,True)</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4045,7 +4057,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>丁番地</t>
+          <t>市区町村</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4055,17 +4067,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>入力/必須/60字</t>
+          <t>英字+記号/大文字/半角/スペース/trim</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>全バリデーション</t>
+          <t>全変換</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>setupAddrField(60,True)</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -4083,115 +4095,111 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
+          <t>市区町村</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>エラーメッセージ</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>.red-hint又はerr要素</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>市区町村</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>エラー時ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn()</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>丁番地</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>英字+記号/大文字/半角/スペース/trim</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>全変換</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>丁番地</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>エラーメッセージ</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>.red-hint又はerr要素</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>err要素なし</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>丁番地</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>入力/必須/60字</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>全バリデーション</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>setupAddrField(60,True)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4201,7 +4209,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>建物名</t>
+          <t>丁番地</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4211,12 +4219,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>入力/任意/60字/英数字記号</t>
+          <t>英字+記号/大文字/半角/スペース/trim</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>全変換</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4239,115 +4247,115 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
+          <t>丁番地</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>エラーメッセージ</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>errStreet追加</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>error div追加済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>丁番地</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>エラー時ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn()</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>建物名</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>大文字/半角変換/スペース処理</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>全変換</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>入力/任意/60字/英数字記号</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>建物名</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>エラーメッセージ</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>err要素なし</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>red-hint未設置</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>建物名</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4357,7 +4365,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>部屋番号</t>
+          <t>建物名</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4367,12 +4375,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>入力/任意/10字/英数字記号</t>
+          <t>大文字/半角変換/スペース処理</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>全変換</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4395,125 +4403,125 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
+          <t>建物名</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>エラーメッセージ</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>errBuilding追加</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>error div追加済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>建物名</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>エラー時ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>updateBtn()</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>部屋番号</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>大文字/半角変換/スペース処理</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>全変換</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>入力/任意/10字/英数字記号</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>部屋番号</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>エラー表示</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>エラーメッセージ</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>err要素なし</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>red-hint未設置</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>住所情報</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>部屋番号</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>エラー時ボタン非アクティブ</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>disabled</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>未実装</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>パスポート情報</t>
+          <t>住所情報</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>パスポートアップロード</t>
+          <t>部屋番号</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4523,17 +4531,17 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>必須/ファイル選択</t>
+          <t>大文字/半角変換/スペース処理</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>jpg,jpeg,png,gif</t>
+          <t>全変換</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>accept属性</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4546,12 +4554,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>パスポート情報</t>
+          <t>住所情報</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>パスポートアップロード</t>
+          <t>部屋番号</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4561,17 +4569,17 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>サイズ上限10MB</t>
+          <t>エラー表示</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>ファイルサイズチェック</t>
+          <t>エラーメッセージ</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>file.size&gt;10*1024*1024</t>
+          <t>errUnit追加</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -4579,17 +4587,21 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>error div追加済み</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>パスポート情報</t>
+          <t>住所情報</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>パスポートアップロード</t>
+          <t>部屋番号</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4599,17 +4611,17 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>ファイル名表示</t>
+          <t>エラー時ボタン非アクティブ</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>選択後に名前表示</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>passportFileName</t>
+          <t>updateBtn()</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4637,17 +4649,17 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>必須/ファイル選択</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>※パスポートの顔写真ページ…</t>
+          <t>jpg,jpeg,png,gif</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>.hint実装</t>
+          <t>accept属性</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4665,7 +4677,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>顔写真アップロード</t>
+          <t>パスポートアップロード</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4675,17 +4687,17 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>必須/ファイル選択</t>
+          <t>サイズ上限10MB</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>jpeg,png</t>
+          <t>ファイルサイズチェック</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>accept属性</t>
+          <t>file.size&gt;10*1024*1024</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4703,7 +4715,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>顔写真アップロード</t>
+          <t>パスポートアップロード</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4713,17 +4725,17 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>サイズ上限10MB</t>
+          <t>ファイル名表示</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>ファイルサイズチェック</t>
+          <t>選択後に名前表示</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>file.size&gt;10*1024*1024</t>
+          <t>passportFileName</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4741,7 +4753,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>顔写真アップロード</t>
+          <t>パスポートアップロード</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4751,17 +4763,17 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>ファイル形式チェック</t>
+          <t>注記</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>jpeg/pngのみ</t>
+          <t>※パスポートの顔写真ページ…</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>validTypes</t>
+          <t>.hint実装</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4789,17 +4801,17 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>パスポート写真不可注記</t>
+          <t>必須/ファイル選択</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>※パスポート顔写真は使用不可</t>
+          <t>jpeg,png</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>.hint(赤)</t>
+          <t>accept属性</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4817,7 +4829,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>パスポート番号</t>
+          <t>顔写真アップロード</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4827,17 +4839,17 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>入力/必須</t>
+          <t>サイズ上限10MB</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>テキスト</t>
+          <t>ファイルサイズチェック</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>input id=passportNum</t>
+          <t>file.size&gt;10*1024*1024</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4855,7 +4867,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>パスポート番号</t>
+          <t>顔写真アップロード</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4865,17 +4877,17 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>プレースホルダー</t>
+          <t>ファイル形式チェック</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>(例) TH1234567</t>
+          <t>jpeg/pngのみ</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>placeholder実装</t>
+          <t>validTypes</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4893,7 +4905,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>パスポート番号</t>
+          <t>顔写真アップロード</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4903,17 +4915,17 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>パスポート写真不可注記</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>※O(オー)と0(ゼロ)の混同注意</t>
+          <t>※パスポート顔写真は使用不可</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>.hint実装</t>
+          <t>.hint(赤)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4931,7 +4943,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>パスポート番号</t>
+          <t>顔写真アップロード</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4941,17 +4953,17 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>国籍別バリデーション</t>
+          <t>解像度チェック</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>41カ国+フォールバック</t>
+          <t>600-2400px</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>PASS_REGEX実装</t>
+          <t>Image onload width/height検証</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4959,7 +4971,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>範囲外でエラー表示</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4979,17 +4995,17 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>自動大文字変換</t>
+          <t>入力/必須</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>toUpperCase</t>
+          <t>テキスト</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>input id=passportNum</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -5017,17 +5033,17 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>エラー表示</t>
+          <t>プレースホルダー</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>パスポート番号に誤りがあります</t>
+          <t>(例) TH1234567</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>errPassportNum</t>
+          <t>placeholder実装</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -5045,7 +5061,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>発行年月日</t>
+          <t>パスポート番号</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5055,17 +5071,17 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須</t>
+          <t>注記</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Day/Month/Year</t>
+          <t>※O(オー)と0(ゼロ)の混同注意</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>select実装</t>
+          <t>.hint実装</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -5083,7 +5099,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>発行年月日</t>
+          <t>パスポート番号</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -5093,17 +5109,17 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>論理チェック</t>
+          <t>国籍別バリデーション</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>発行日&gt;DOB &amp; ≤今日</t>
+          <t>41カ国+フォールバック</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>checkPassportDates</t>
+          <t>PASS_REGEX実装</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -5121,7 +5137,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>有効期間満了日</t>
+          <t>パスポート番号</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -5131,17 +5147,17 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須</t>
+          <t>自動大文字変換</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Day/Month/Year</t>
+          <t>toUpperCase</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>select実装</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -5159,7 +5175,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>有効期間満了日</t>
+          <t>パスポート番号</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -5169,17 +5185,17 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>論理チェック</t>
+          <t>エラー表示</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>有効期限&gt;今日</t>
+          <t>パスポート番号に誤りがあります</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>checkPassportDates</t>
+          <t>errPassportNum</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -5197,7 +5213,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>有効期間満了日</t>
+          <t>発行年月日</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -5207,17 +5223,17 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>JPN期間チェック</t>
+          <t>プルダウン/必須</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>T=10年/M=5年</t>
+          <t>Day/Month/Year</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>prefix T/M判定</t>
+          <t>select実装</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -5235,7 +5251,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>有効期間満了日</t>
+          <t>発行年月日</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -5245,17 +5261,17 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>訂正旅券注記</t>
+          <t>論理チェック</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>期間不一致時に注記表示</t>
+          <t>発行日&gt;DOB &amp; ≤今日</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>correctedPassportNote</t>
+          <t>checkPassportDates</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -5273,7 +5289,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>発行国</t>
+          <t>有効期間満了日</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5283,17 +5299,17 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須/デフォルトJPN</t>
+          <t>プルダウン/必須</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>国籍と連動</t>
+          <t>Day/Month/Year</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>custom-select issuingCountry</t>
+          <t>select実装</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -5311,7 +5327,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>発行国</t>
+          <t>有効期間満了日</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -5321,17 +5337,17 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>論理チェック</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>※通常は国籍と同じ</t>
+          <t>有効期限&gt;今日</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>.hint実装</t>
+          <t>checkPassportDates</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -5349,7 +5365,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>訂正旅券</t>
+          <t>有効期間満了日</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5359,17 +5375,17 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>トグル</t>
+          <t>JPN期間チェック</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>該当する/該当しない</t>
+          <t>T=10年/M=5年</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>radio corrPassYes/No</t>
+          <t>prefix T/M判定</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -5387,7 +5403,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>出生国</t>
+          <t>有効期間満了日</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -5397,17 +5413,17 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須/デフォルトJPN</t>
+          <t>訂正旅券注記</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>世界各国リスト</t>
+          <t>期間不一致時に注記表示</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>custom-select birthCountry</t>
+          <t>correctedPassportNote</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -5425,7 +5441,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>出生都市</t>
+          <t>発行国</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5435,17 +5451,17 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>入力/任意</t>
+          <t>プルダウン/必須/デフォルトJPN</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>テキスト</t>
+          <t>国籍と連動</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>input id=birthCity</t>
+          <t>custom-select issuingCountry</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -5463,7 +5479,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>出生都市</t>
+          <t>発行国</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -5473,17 +5489,17 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>プレースホルダー/注記</t>
+          <t>注記</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>(例) TOKYO・空欄でも可</t>
+          <t>※通常は国籍と同じ</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>.hint実装</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -5501,7 +5517,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>出生都市</t>
+          <t>訂正旅券</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -5511,17 +5527,17 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>エラー表示</t>
+          <t>トグル</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>半角英数字で入力してください</t>
+          <t>該当する/該当しない</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>errBirthCity</t>
+          <t>radio corrPassYes/No</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -5539,7 +5555,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>他国パスポート有無</t>
+          <t>出生国</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -5549,17 +5565,17 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>トグル/必須/デフォルトNo</t>
+          <t>プルダウン/必須/デフォルトJPN</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
+          <t>世界各国リスト</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>radio実装</t>
+          <t>custom-select birthCountry</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -5577,7 +5593,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>他国パスポート有無</t>
+          <t>出生都市</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -5587,17 +5603,17 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Yes→詳細表示</t>
+          <t>入力/任意</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>otherPassFields</t>
+          <t>テキスト</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>input id=birthCity</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -5615,7 +5631,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>他国パスポート(発給国)</t>
+          <t>出生都市</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -5625,17 +5641,17 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須</t>
+          <t>プレースホルダー/注記</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>世界各国リスト</t>
+          <t>(例) TOKYO・空欄でも可</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>custom-select</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -5653,7 +5669,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>他国パスポート(種類)</t>
+          <t>出生都市</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5663,17 +5679,17 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須</t>
+          <t>エラー表示</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>パスポート/国家身分証明書</t>
+          <t>半角英数字で入力してください</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>select docType</t>
+          <t>errBirthCity</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -5691,7 +5707,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>他国パスポート(ID番号)</t>
+          <t>他国パスポート有無</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -5701,17 +5717,17 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>入力/必須/英数字</t>
+          <t>トグル/必須/デフォルトNo</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>はい/いいえ</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>errDocId</t>
+          <t>radio実装</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5729,7 +5745,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>他国パスポート(有効期限)</t>
+          <t>他国パスポート有無</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5739,17 +5755,17 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須</t>
+          <t>Yes→詳細表示</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>年選択+UNKNOWN</t>
+          <t>otherPassFields</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>select実装</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5767,7 +5783,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>他国籍(現在)</t>
+          <t>他国パスポート(発給国)</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -5777,17 +5793,17 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>トグル/必須/デフォルトNo</t>
+          <t>プルダウン/必須</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>はい/いいえ</t>
+          <t>世界各国リスト</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>radio実装</t>
+          <t>custom-select</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5805,7 +5821,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>他国籍(現在)</t>
+          <t>他国パスポート(種類)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5815,17 +5831,17 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Yes→詳細表示</t>
+          <t>プルダウン/必須</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>国選択+取得経緯</t>
+          <t>パスポート/国家身分証明書</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>実装済み</t>
+          <t>select docType</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -5843,7 +5859,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>他国籍(現在)国</t>
+          <t>他国パスポート(ID番号)</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -5853,17 +5869,17 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須</t>
+          <t>入力/必須/英数字</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>世界各国リスト</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>custom-select</t>
+          <t>errDocId</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5881,7 +5897,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>他国籍(現在)取得経緯</t>
+          <t>他国パスポート(有効期限)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5896,12 +5912,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>出生/両親/帰化/その他</t>
+          <t>年選択+UNKNOWN</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>select curNatHow</t>
+          <t>select実装</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -5919,7 +5935,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>他国籍(過去)</t>
+          <t>他国籍(現在)</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -5957,7 +5973,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>他国籍(過去)</t>
+          <t>他国籍(現在)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -5972,7 +5988,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>国選択+取得日+放棄日</t>
+          <t>国選択+取得経緯</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -5995,7 +6011,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>他国籍(過去)国</t>
+          <t>他国籍(現在)国</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -6033,7 +6049,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>他国籍(過去)取得日</t>
+          <t>他国籍(現在)国</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6043,17 +6059,17 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>プルダウン/必須</t>
+          <t>制限国エラー</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Day/Month/Year</t>
+          <t>IRN/IRQ/SDN/SYR/PRK</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>select実装</t>
+          <t>checkDualRestriction()</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -6061,7 +6077,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>VWP対象外警告表示</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -6071,7 +6091,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>他国籍(過去)放棄日</t>
+          <t>他国籍(現在)取得経緯</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -6086,12 +6106,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Day/Month/Year</t>
+          <t>出生/両親/帰化/その他</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>select実装</t>
+          <t>select curNatHow</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -6109,7 +6129,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>GE/NEXUS/SENTRI</t>
+          <t>他国籍(過去)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -6147,7 +6167,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>GE/NEXUS/SENTRI</t>
+          <t>他国籍(過去)</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -6157,17 +6177,17 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>注記</t>
+          <t>Yes→詳細表示</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>※ご存知でない方は「いいえ」</t>
+          <t>国選択+取得日+放棄日</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>.note実装</t>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -6185,7 +6205,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>GE/NEXUS/SENTRI</t>
+          <t>他国籍(過去)国</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -6195,17 +6215,17 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Yes→PASS ID表示</t>
+          <t>プルダウン/必須</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>9桁数字</t>
+          <t>世界各国リスト</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>input passId</t>
+          <t>custom-select</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -6223,38 +6243,270 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
+          <t>他国籍(過去)国</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>制限国エラー</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>IRN/IRQ/SDN/SYR/PRK</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>checkDualRestriction()</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>VWP対象外警告表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>他国籍(過去)取得日</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>プルダウン/必須</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Day/Month/Year</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>select実装</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>他国籍(過去)放棄日</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>プルダウン/必須</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Day/Month/Year</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>select実装</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>GE/NEXUS/SENTRI</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>トグル/必須/デフォルトNo</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>はい/いいえ</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>radio実装</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>GE/NEXUS/SENTRI</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>※ご存知でない方は「いいえ」</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>.note実装</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>GE/NEXUS/SENTRI</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Yes→PASS ID表示</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>9桁数字</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>input passId</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>GE PASS ID</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>入力/必須/9桁数字</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>errPassId</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H151"/>
+  <autoFilter ref="A1:H157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/step1-validation-check.xlsx
+++ b/step1-validation-check.xlsx
@@ -1362,44 +1362,44 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>姓</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>苗字チェックアラート</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>候補にない場合アラート</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>未実装</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>苗字辞書データが必要</t>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>486件の日本人姓辞書 + レーベンシュタイン距離(編集距離1-2)でアラート表示</t>
         </is>
       </c>
     </row>
@@ -2012,44 +2012,44 @@
       <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>申請者情報</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>姓(別名)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>苗字チェックアラート</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>候補にない場合アラート</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>未実装</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>苗字辞書データが必要</t>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>486件の日本人姓辞書 + レーベンシュタイン距離(編集距離1-2)でアラート表示</t>
         </is>
       </c>
     </row>
